--- a/Plotting/Results_excels/result_data_long_Scope1-3.xlsx
+++ b/Plotting/Results_excels/result_data_long_Scope1-3.xlsx
@@ -559,32 +559,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20250905_09_38\Iteration_1\20250905134015_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20251112_10_21\Iteration_1\20251112140018_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20250905_09_38\Iteration_1\20250905144159_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20251112_10_21\Iteration_1\20251112150037_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20250905_09_38\Iteration_1\20250905232015_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20251112_10_21\Iteration_1\20251113202321_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20250905_09_38\Iteration_2\20250906030625_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20251112_10_21\Iteration_2\20251114000120_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20250905_09_38\Iteration_2\20250906040250_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20251112_10_21\Iteration_2\20251114010350_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20250905_09_38\Iteration_2\20250906104935_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\Scope1-3\Results_model_linking_20251112_10_21\Iteration_2\20251114062009_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
     </row>
@@ -604,22 +604,22 @@
         <v>1588224754.870359</v>
       </c>
       <c r="E5" t="n">
-        <v>3792767335.094356</v>
+        <v>3794643805.36243</v>
       </c>
       <c r="F5" t="n">
-        <v>2542070204.02573</v>
+        <v>2539902624.896738</v>
       </c>
       <c r="G5" t="n">
-        <v>2067421889.974788</v>
+        <v>2068814331.811039</v>
       </c>
       <c r="H5" t="n">
-        <v>3801602146.29517</v>
+        <v>3801164446.633963</v>
       </c>
       <c r="I5" t="n">
-        <v>2538046273.867115</v>
+        <v>2537258731.658308</v>
       </c>
       <c r="J5" t="n">
-        <v>2069010705.972322</v>
+        <v>2064053482.815187</v>
       </c>
     </row>
     <row r="6">
@@ -637,17 +637,17 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>410926708.5949293</v>
+        <v>416130112.0627208</v>
       </c>
       <c r="G6" t="n">
-        <v>577708513.5500331</v>
+        <v>580956268.8975383</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>411517740.8323417</v>
+        <v>414943647.7740746</v>
       </c>
       <c r="J6" t="n">
-        <v>578561039.8559222</v>
+        <v>581667230.9220307</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +666,22 @@
         <v>1967451280.173568</v>
       </c>
       <c r="E7" t="n">
-        <v>3792767335.094356</v>
+        <v>3794643805.36243</v>
       </c>
       <c r="F7" t="n">
-        <v>2952996912.620659</v>
+        <v>2956032736.959459</v>
       </c>
       <c r="G7" t="n">
-        <v>2645130403.524821</v>
+        <v>2649770600.708577</v>
       </c>
       <c r="H7" t="n">
-        <v>3801602146.29517</v>
+        <v>3801164446.633963</v>
       </c>
       <c r="I7" t="n">
-        <v>2949564014.699457</v>
+        <v>2952202379.432383</v>
       </c>
       <c r="J7" t="n">
-        <v>2647571745.828244</v>
+        <v>2645720713.737218</v>
       </c>
     </row>
     <row r="8">
@@ -698,12 +698,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>89799679426.44908</v>
+        <v>89843170309.67746</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>89872201659.90529</v>
+        <v>89841438920.29491</v>
       </c>
     </row>
     <row r="9">
@@ -722,22 +722,22 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6299984.707260767</v>
+        <v>6305411.847687604</v>
       </c>
       <c r="F9" t="n">
-        <v>3149992.353630414</v>
+        <v>3152705.923843806</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.271255314350128e-06</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>6304544.707618851</v>
+        <v>6304163.871998057</v>
       </c>
       <c r="I9" t="n">
-        <v>3152272.35380942</v>
+        <v>3152081.935999059</v>
       </c>
       <c r="J9" t="n">
-        <v>3.576278686523438e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -756,22 +756,22 @@
         <v>109669566.8429292</v>
       </c>
       <c r="E10" t="n">
-        <v>410926708.5949293</v>
+        <v>416130112.0627208</v>
       </c>
       <c r="F10" t="n">
-        <v>166781804.9551038</v>
+        <v>164826156.8348175</v>
       </c>
       <c r="G10" t="n">
-        <v>108917118.8722222</v>
+        <v>110378183.520891</v>
       </c>
       <c r="H10" t="n">
-        <v>411517740.8323417</v>
+        <v>414943647.7740746</v>
       </c>
       <c r="I10" t="n">
-        <v>167043299.0235806</v>
+        <v>166723583.1479561</v>
       </c>
       <c r="J10" t="n">
-        <v>110571283.3077637</v>
+        <v>109262146.1380113</v>
       </c>
     </row>
     <row r="11">
@@ -790,22 +790,22 @@
         <v>234380321.476349</v>
       </c>
       <c r="E11" t="n">
-        <v>283007335.4437639</v>
+        <v>283712429.719788</v>
       </c>
       <c r="F11" t="n">
-        <v>248424525.6158753</v>
+        <v>248615374.944479</v>
       </c>
       <c r="G11" t="n">
-        <v>272364811.0343158</v>
+        <v>272919987.1270174</v>
       </c>
       <c r="H11" t="n">
-        <v>283200860.8739171</v>
+        <v>283256017.9324558</v>
       </c>
       <c r="I11" t="n">
-        <v>248613151.4285068</v>
+        <v>248590590.46641</v>
       </c>
       <c r="J11" t="n">
-        <v>273011622.1497286</v>
+        <v>272626287.9263911</v>
       </c>
     </row>
     <row r="12">
@@ -824,22 +824,22 @@
         <v>1244174866.551081</v>
       </c>
       <c r="E12" t="n">
-        <v>2140605617.081296</v>
+        <v>2135748121.546649</v>
       </c>
       <c r="F12" t="n">
-        <v>1647750036.467566</v>
+        <v>1646934522.100799</v>
       </c>
       <c r="G12" t="n">
-        <v>1686139960.068449</v>
+        <v>1685516161.16318</v>
       </c>
       <c r="H12" t="n">
-        <v>2147962294.560109</v>
+        <v>2144101455.996539</v>
       </c>
       <c r="I12" t="n">
-        <v>1642929198.400615</v>
+        <v>1642512895.578487</v>
       </c>
       <c r="J12" t="n">
-        <v>1685427800.514784</v>
+        <v>1682165048.750738</v>
       </c>
     </row>
     <row r="13">
@@ -858,22 +858,22 @@
         <v>6.984919309616089e-10</v>
       </c>
       <c r="E13" t="n">
-        <v>958227673.974367</v>
+        <v>959053142.0332723</v>
       </c>
       <c r="F13" t="n">
-        <v>479113836.9871848</v>
+        <v>479526571.0166427</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0001987814903259277</v>
+        <v>-4.947185516357422e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>958921250.0288024</v>
+        <v>958863324.930894</v>
       </c>
       <c r="I13" t="n">
-        <v>479460625.0144131</v>
+        <v>479431662.4654551</v>
       </c>
       <c r="J13" t="n">
-        <v>4.518032073974609e-05</v>
+        <v>4.571676254272461e-05</v>
       </c>
     </row>
     <row r="14">
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>31.07570449028047</v>
+        <v>30.92357830069739</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>29.96706859483574</v>
+        <v>30.27516124847167</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -960,22 +960,22 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>341.9117647058839</v>
+        <v>341.9117647058953</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>308.6521324044054</v>
+        <v>309.1975841798381</v>
       </c>
       <c r="H16" t="n">
-        <v>341.911764705882</v>
+        <v>341.9117647058825</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>309.5408777861256</v>
+        <v>308.058441076677</v>
       </c>
     </row>
     <row r="17">
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000002</v>
       </c>
     </row>
     <row r="18">
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>563.3634687205019</v>
+        <v>563.0112486284431</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>563.9610728014717</v>
+        <v>561.4390354556768</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>447.7629652852092</v>
+        <v>447.5355536170992</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>448.1488096592267</v>
+        <v>446.5204507642445</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1099,19 +1099,19 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>90.33677916371849</v>
+        <v>91.15848873778754</v>
       </c>
       <c r="G20" t="n">
-        <v>94.09808566704852</v>
+        <v>93.43101167131789</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>90.55478184226945</v>
+        <v>89.91267914351354</v>
       </c>
       <c r="J20" t="n">
-        <v>94.13204230421472</v>
+        <v>94.3538741958421</v>
       </c>
     </row>
     <row r="21">
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3407.405902240549</v>
+        <v>3404.145946637391</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3412.936997189905</v>
+        <v>3389.594405548295</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>894.2648774181429</v>
+        <v>889.8871453438098</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>862.3616861823233</v>
+        <v>871.2276618265228</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>634.4987639959961</v>
+        <v>633.9970535688952</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>635.3500050398176</v>
+        <v>631.7575568435926</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1558,22 +1558,22 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>637.1849037189876</v>
+        <v>636.5752920211844</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>94.04288158858695</v>
+        <v>93.27278943642818</v>
       </c>
       <c r="H35" t="n">
-        <v>638.2192184745122</v>
+        <v>633.854153837542</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>93.92900370793613</v>
+        <v>92.18696168595457</v>
       </c>
     </row>
     <row r="36">
@@ -1670,19 +1670,19 @@
         <v>0.9104843470844927</v>
       </c>
       <c r="E39" t="n">
-        <v>123.8804683087842</v>
+        <v>123.8655870541176</v>
       </c>
       <c r="F39" t="n">
-        <v>3.085608016851402</v>
+        <v>3.147117891480479</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>123.9024346221356</v>
+        <v>123.7049115822417</v>
       </c>
       <c r="I39" t="n">
-        <v>3.139977708818485</v>
+        <v>3.28860554405542</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>63.12236862348283</v>
+        <v>300.7287446379989</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>64.43734791714601</v>
+        <v>313.2329257251197</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>29674.51371381121</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>31.95816639161903</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1919,13 +1919,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-3.717181163591263e-11</v>
       </c>
       <c r="I47" t="n">
-        <v>3.695318241823908e-10</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>2.105531201642726e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1947,19 +1947,19 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>179.3755492104561</v>
+        <v>178.502582779882</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7019532904162008</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>172.948306977077</v>
+        <v>174.735242278135</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>36.87990425366607</v>
       </c>
     </row>
     <row r="49">
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4912.360355477428</v>
+        <v>4908.872988205776</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>4918.277294800439</v>
+        <v>4893.306344264342</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>637.1849037189922</v>
+        <v>636.5752920211844</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>638.2192184745122</v>
+        <v>633.854153837542</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
         <v>214.2356823779513</v>
       </c>
       <c r="E53" t="n">
-        <v>162.8074891447258</v>
+        <v>194.765655536565</v>
       </c>
       <c r="F53" t="n">
-        <v>207.6162209204372</v>
+        <v>233.3737872370637</v>
       </c>
       <c r="G53" t="n">
-        <v>462.3317150382052</v>
+        <v>474.43125127734</v>
       </c>
       <c r="H53" t="n">
-        <v>162.8074891445043</v>
+        <v>162.8074891451424</v>
       </c>
       <c r="I53" t="n">
-        <v>196.6509498303346</v>
+        <v>229.2314370697584</v>
       </c>
       <c r="J53" t="n">
-        <v>442.6652452296829</v>
+        <v>441.8374610496472</v>
       </c>
     </row>
     <row r="54">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3.367295860135484e-10</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -2454,22 +2454,22 @@
         <v>128.0211414631145</v>
       </c>
       <c r="E63" t="n">
-        <v>123.8804683087842</v>
+        <v>123.8655870541176</v>
       </c>
       <c r="F63" t="n">
-        <v>126.9660763256683</v>
+        <v>127.0127049456039</v>
       </c>
       <c r="G63" t="n">
-        <v>126.9660763256356</v>
+        <v>127.0127049455981</v>
       </c>
       <c r="H63" t="n">
-        <v>123.9024346221356</v>
+        <v>123.7049115822417</v>
       </c>
       <c r="I63" t="n">
-        <v>127.0424123309595</v>
+        <v>126.9935171263416</v>
       </c>
       <c r="J63" t="n">
-        <v>127.0424123309541</v>
+        <v>126.9935171262971</v>
       </c>
     </row>
     <row r="64">
@@ -2522,22 +2522,22 @@
         <v>140.7223740019584</v>
       </c>
       <c r="E65" t="n">
-        <v>135.1598173516658</v>
+        <v>135.1598173520543</v>
       </c>
       <c r="F65" t="n">
-        <v>150.236499406248</v>
+        <v>149.5010404177601</v>
       </c>
       <c r="G65" t="n">
-        <v>150.236499406248</v>
+        <v>135.213774208132</v>
       </c>
       <c r="H65" t="n">
-        <v>135.1598173515993</v>
+        <v>135.1598173516549</v>
       </c>
       <c r="I65" t="n">
-        <v>144.8767632786303</v>
+        <v>146.3662471868558</v>
       </c>
       <c r="J65" t="n">
-        <v>135.2245212816278</v>
+        <v>135.2173124370065</v>
       </c>
     </row>
     <row r="66">
@@ -2556,22 +2556,22 @@
         <v>553.0795362339358</v>
       </c>
       <c r="E66" t="n">
-        <v>341.9117647060357</v>
+        <v>341.911764706698</v>
       </c>
       <c r="F66" t="n">
-        <v>318.6482510184088</v>
+        <v>321.5466974877867</v>
       </c>
       <c r="G66" t="n">
-        <v>650.5638971102892</v>
+        <v>651.1093488857334</v>
       </c>
       <c r="H66" t="n">
-        <v>341.9117647058821</v>
+        <v>341.9117647058825</v>
       </c>
       <c r="I66" t="n">
-        <v>319.417219902185</v>
+        <v>317.1523073845275</v>
       </c>
       <c r="J66" t="n">
-        <v>651.4526424920077</v>
+        <v>649.9702057825596</v>
       </c>
     </row>
     <row r="67">
@@ -2692,22 +2692,22 @@
         <v>4600</v>
       </c>
       <c r="E70" t="n">
-        <v>1720.621992665878</v>
+        <v>1900</v>
       </c>
       <c r="F70" t="n">
         <v>3250</v>
       </c>
       <c r="G70" t="n">
-        <v>3090.142010761912</v>
+        <v>3322.097851474702</v>
       </c>
       <c r="H70" t="n">
-        <v>1724.201759502443</v>
+        <v>1900</v>
       </c>
       <c r="I70" t="n">
-        <v>3250.000000000007</v>
+        <v>3250</v>
       </c>
       <c r="J70" t="n">
-        <v>3120.475552677004</v>
+        <v>3350.982359441538</v>
       </c>
     </row>
     <row r="71">
@@ -2862,22 +2862,22 @@
         <v>80.71197007483882</v>
       </c>
       <c r="E75" t="n">
-        <v>84.2351262819214</v>
+        <v>84.08544651648</v>
       </c>
       <c r="F75" t="n">
-        <v>85.93796472421548</v>
+        <v>84.78249558089419</v>
       </c>
       <c r="G75" t="n">
-        <v>159.3615116267022</v>
+        <v>158.9566099815247</v>
       </c>
       <c r="H75" t="n">
-        <v>84.49236703092464</v>
+        <v>83.51156706245672</v>
       </c>
       <c r="I75" t="n">
-        <v>86.5137482663111</v>
+        <v>85.60037027243064</v>
       </c>
       <c r="J75" t="n">
-        <v>160.8759328651835</v>
+        <v>159.8318801764134</v>
       </c>
     </row>
     <row r="76">
@@ -3032,22 +3032,22 @@
         <v>322.7818378213971</v>
       </c>
       <c r="E80" t="n">
-        <v>4912.360355478194</v>
+        <v>4908.87298820648</v>
       </c>
       <c r="F80" t="n">
-        <v>2322.189896781737</v>
+        <v>2390.0037517588</v>
       </c>
       <c r="G80" t="n">
-        <v>1362.96236089622</v>
+        <v>1744.118829280034</v>
       </c>
       <c r="H80" t="n">
-        <v>4918.277294800453</v>
+        <v>4893.306344264342</v>
       </c>
       <c r="I80" t="n">
-        <v>2291.880643152502</v>
+        <v>2374.949785397889</v>
       </c>
       <c r="J80" t="n">
-        <v>1748.155227773275</v>
+        <v>1737.250364471205</v>
       </c>
     </row>
     <row r="81">
@@ -3409,16 +3409,16 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>9.833836407775635</v>
+        <v>9.955537359442104</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>9.708321212010807e-11</v>
       </c>
       <c r="I91" t="n">
-        <v>10.72074512413143</v>
+        <v>10.47427100122268</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>2.728484105318785e-12</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -3847,17 +3847,17 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>563.3634687205019</v>
+        <v>563.0112486284431</v>
       </c>
       <c r="G104" t="n">
-        <v>563.3634687205019</v>
+        <v>563.0112486284431</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>563.9610728014717</v>
+        <v>561.4390354556768</v>
       </c>
       <c r="J104" t="n">
-        <v>563.9610728014717</v>
+        <v>561.4390354556768</v>
       </c>
     </row>
     <row r="105">
@@ -3875,17 +3875,17 @@
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>447.7629652852092</v>
+        <v>447.5355536170992</v>
       </c>
       <c r="G105" t="n">
-        <v>447.7629652852092</v>
+        <v>447.5355536170992</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>448.1488096592267</v>
+        <v>446.5204507642445</v>
       </c>
       <c r="J105" t="n">
-        <v>448.1488096592267</v>
+        <v>446.5204507642445</v>
       </c>
     </row>
     <row r="106">
@@ -3903,17 +3903,17 @@
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>183.4684231070427</v>
+        <v>181.2273293569164</v>
       </c>
       <c r="G106" t="n">
-        <v>3.575192176585623</v>
+        <v>5.267742513184345</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>184.2312491948843</v>
+        <v>183.8130880740515</v>
       </c>
       <c r="J106" t="n">
-        <v>5.275906208657349</v>
+        <v>4.477203009837121</v>
       </c>
     </row>
     <row r="107">
@@ -3979,17 +3979,17 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>123.8804683087842</v>
+        <v>123.8655870541176</v>
       </c>
       <c r="G109" t="n">
-        <v>126.9660763256356</v>
+        <v>127.0127049455981</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>123.9024346221356</v>
+        <v>123.7049115822417</v>
       </c>
       <c r="J109" t="n">
-        <v>127.0424123309541</v>
+        <v>126.9935171262971</v>
       </c>
     </row>
     <row r="110">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>4912.360355477428</v>
+        <v>4908.872988205776</v>
       </c>
       <c r="G110" t="n">
-        <v>4912.360355477428</v>
+        <v>4908.872988205776</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>4918.277294800439</v>
+        <v>4893.306344264342</v>
       </c>
       <c r="J110" t="n">
-        <v>4918.277294800439</v>
+        <v>4893.306344264342</v>
       </c>
     </row>
     <row r="111">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>341.9117647058839</v>
+        <v>341.9117647058953</v>
       </c>
       <c r="G112" t="n">
-        <v>341.9117647058839</v>
+        <v>341.9117647058953</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>341.911764705882</v>
+        <v>341.9117647058825</v>
       </c>
       <c r="J112" t="n">
-        <v>341.911764705882</v>
+        <v>341.9117647058825</v>
       </c>
     </row>
     <row r="113">
@@ -4077,17 +4077,17 @@
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="G113" t="n">
         <v>0.9</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="J113" t="n">
         <v>0.9</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0.9000000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -4104,12 +4104,12 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>90.33677916371849</v>
+        <v>91.15848873778754</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>90.55478184226945</v>
+        <v>89.91267914351354</v>
       </c>
     </row>
     <row r="115">
@@ -4126,12 +4126,12 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>183.4684231070427</v>
+        <v>181.2273293569164</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>184.2312491948843</v>
+        <v>183.8130880740515</v>
       </c>
     </row>
     <row r="116">
@@ -4165,17 +4165,17 @@
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>634.4987639959961</v>
+        <v>633.9970535688952</v>
       </c>
       <c r="G117" t="n">
-        <v>634.4987639959961</v>
+        <v>633.9970535688952</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>635.3500050398176</v>
+        <v>631.7575568435926</v>
       </c>
       <c r="J117" t="n">
-        <v>635.3500050398176</v>
+        <v>631.7575568435926</v>
       </c>
     </row>
     <row r="118">
@@ -4190,8 +4190,12 @@
         <v>15.63745999133647</v>
       </c>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>31.95816639161903</v>
+      </c>
+      <c r="G118" t="n">
+        <v>31.95816639161903</v>
+      </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
@@ -4212,9 +4216,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="n">
-        <v>3.695318241823908e-10</v>
-      </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -4227,17 +4229,17 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
-        <v>3407.405902240549</v>
+        <v>3404.145946637391</v>
       </c>
       <c r="G120" t="n">
-        <v>3407.405902240549</v>
+        <v>3404.145946637391</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>3412.936997189905</v>
+        <v>3389.594405548295</v>
       </c>
       <c r="J120" t="n">
-        <v>3412.936997189905</v>
+        <v>3389.594405548295</v>
       </c>
     </row>
     <row r="121">
@@ -4251,17 +4253,17 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>637.1849037189876</v>
+        <v>636.5752920211844</v>
       </c>
       <c r="G121" t="n">
-        <v>637.1849037189876</v>
+        <v>636.5752920211844</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>638.2192184745122</v>
+        <v>633.854153837542</v>
       </c>
       <c r="J121" t="n">
-        <v>638.2192184745122</v>
+        <v>633.854153837542</v>
       </c>
     </row>
     <row r="122">
@@ -4275,17 +4277,17 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>63.12236862348283</v>
+        <v>300.7287446379989</v>
       </c>
       <c r="G122" t="n">
-        <v>63.12236862348283</v>
+        <v>300.7287446379989</v>
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>64.43734791714601</v>
+        <v>313.2329257251197</v>
       </c>
       <c r="J122" t="n">
-        <v>64.43734791714601</v>
+        <v>313.2329257251197</v>
       </c>
     </row>
     <row r="123">
@@ -4299,17 +4301,17 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>637.1849037189922</v>
+        <v>636.5752920211844</v>
       </c>
       <c r="G123" t="n">
-        <v>637.1849037189922</v>
+        <v>636.5752920211844</v>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>638.2192184745122</v>
+        <v>633.854153837542</v>
       </c>
       <c r="J123" t="n">
-        <v>638.2192184745122</v>
+        <v>633.854153837542</v>
       </c>
     </row>
     <row r="124">
@@ -4324,12 +4326,12 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>31.07570449028047</v>
+        <v>30.92357830069739</v>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
-        <v>29.96706859483574</v>
+        <v>30.27516124847167</v>
       </c>
     </row>
     <row r="125">
@@ -4344,12 +4346,12 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>894.2648774181429</v>
+        <v>889.8871453438098</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
-        <v>862.3616861823233</v>
+        <v>871.2276618265228</v>
       </c>
     </row>
     <row r="126">
@@ -4364,12 +4366,12 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>179.3755492104561</v>
+        <v>178.502582779882</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>172.948306977077</v>
+        <v>174.735242278135</v>
       </c>
     </row>
   </sheetData>
